--- a/artfynd/A 57442-2024 artfynd.xlsx
+++ b/artfynd/A 57442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90903755</v>
+        <v>90903748</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368652.783288564</v>
+        <v>368641</v>
       </c>
       <c r="R2" t="n">
-        <v>6391762.158502854</v>
+        <v>6391925</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +748,9 @@
           <t>2020-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,16 +785,11 @@
         <v>90903749</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368584.1427042646</v>
+        <v>368584</v>
       </c>
       <c r="R3" t="n">
-        <v>6391779.918085839</v>
+        <v>6391780</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,19 +855,9 @@
           <t>2020-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,16 +892,11 @@
         <v>90903750</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -964,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368605.2326816075</v>
+        <v>368605</v>
       </c>
       <c r="R4" t="n">
-        <v>6391751.920749078</v>
+        <v>6391752</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,19 +962,9 @@
           <t>2020-08-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1044,16 +999,11 @@
         <v>90903754</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1086,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368655.2027892685</v>
+        <v>368655</v>
       </c>
       <c r="R5" t="n">
-        <v>6391754.046908698</v>
+        <v>6391754</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,19 +1069,9 @@
           <t>2020-08-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1163,19 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90903756</v>
+        <v>90903755</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1208,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>368659.1925865628</v>
+        <v>368653</v>
       </c>
       <c r="R6" t="n">
-        <v>6391843.886558918</v>
+        <v>6391762</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,19 +1176,9 @@
           <t>2020-08-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,19 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90903757</v>
+        <v>90903756</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1330,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>368659.2321365612</v>
+        <v>368659</v>
       </c>
       <c r="R7" t="n">
-        <v>6391878.158724719</v>
+        <v>6391844</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,19 +1283,9 @@
           <t>2020-08-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1404,6 +1314,419 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>90903757</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Älebacken, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>368659</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6391878</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosöksspår.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>90903758</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Älebacken, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>368683</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6391881</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>90903759</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älebacken, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>368680</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6391880</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosöksspår.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>90903746</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Älebacken, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>368696</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6391946</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57442-2024 artfynd.xlsx
+++ b/artfynd/A 57442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,48 +1633,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90903746</v>
+        <v>135206003</v>
       </c>
       <c r="B11" t="n">
-        <v>97983</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älebacken, Vg</t>
+          <t>Älebackasjö, öster om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368696</v>
+        <v>368586</v>
       </c>
       <c r="R11" t="n">
-        <v>6391946</v>
+        <v>6391820</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,12 +1710,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,15 +1740,112 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>90903746</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Älebacken, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>368696</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6391946</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57442-2024 artfynd.xlsx
+++ b/artfynd/A 57442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903748</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903749</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903750</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903754</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903757</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903758</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1749,6 +1799,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135206003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,8 +1901,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57442-2024 artfynd.xlsx
+++ b/artfynd/A 57442-2024 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135206003</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 57442-2024 artfynd.xlsx
+++ b/artfynd/A 57442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,48 +1683,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90903746</v>
+        <v>135206003</v>
       </c>
       <c r="B11" t="n">
-        <v>97983</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älebacken, Vg</t>
+          <t>Älebackasjö, öster om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368696</v>
+        <v>368586</v>
       </c>
       <c r="R11" t="n">
-        <v>6391946</v>
+        <v>6391820</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,12 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,16 +1790,118 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135206003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>90903746</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Älebacken, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>368696</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6391946</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/90903746</t>
         </is>
@@ -1795,6 +1919,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
